--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.03838624276937</v>
+        <v>1.956237764450022</v>
       </c>
       <c r="D2" t="n">
-        <v>1.699710487124474</v>
+        <v>0.2762029541577271</v>
       </c>
       <c r="E2" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F2" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.30628552507676</v>
+        <v>3.624771397824974</v>
       </c>
       <c r="D3" t="n">
-        <v>22.31589190576873</v>
+        <v>3.626332434687418</v>
       </c>
       <c r="E3" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F3" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.35516950519588</v>
+        <v>10.29521504459433</v>
       </c>
       <c r="D4" t="n">
-        <v>58.47839766808903</v>
+        <v>9.502739621064467</v>
       </c>
       <c r="E4" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F4" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.67913162466197</v>
+        <v>3.52285888900757</v>
       </c>
       <c r="D5" t="n">
-        <v>21.73265580460482</v>
+        <v>3.531556568248284</v>
       </c>
       <c r="E5" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F5" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.43791276541781</v>
+        <v>4.296160824380394</v>
       </c>
       <c r="D6" t="n">
-        <v>26.49501377581185</v>
+        <v>4.305439738569426</v>
       </c>
       <c r="E6" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F6" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.47510340050045</v>
+        <v>9.989704302581323</v>
       </c>
       <c r="D7" t="n">
-        <v>61.52763927196029</v>
+        <v>9.998241381693548</v>
       </c>
       <c r="E7" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F7" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>66.71691660599788</v>
+        <v>10.84149894847466</v>
       </c>
       <c r="D8" t="n">
-        <v>65.43699259593154</v>
+        <v>10.63351129683888</v>
       </c>
       <c r="E8" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F8" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.99396510120441</v>
+        <v>2.924019328945717</v>
       </c>
       <c r="D9" t="n">
-        <v>16.65285833400196</v>
+        <v>2.706089479275319</v>
       </c>
       <c r="E9" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F9" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>89.40206244193325</v>
+        <v>14.52783514681415</v>
       </c>
       <c r="D10" t="n">
-        <v>68.20869935589499</v>
+        <v>11.08391364533294</v>
       </c>
       <c r="E10" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F10" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>64.39516067517539</v>
+        <v>10.464213609716</v>
       </c>
       <c r="D11" t="n">
-        <v>49.19808744972672</v>
+        <v>7.994689210580592</v>
       </c>
       <c r="E11" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F11" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>83.89102305790543</v>
+        <v>13.63229124690963</v>
       </c>
       <c r="D12" t="n">
-        <v>58.69412236331676</v>
+        <v>9.537794884038973</v>
       </c>
       <c r="E12" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F12" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>60.69559476696654</v>
+        <v>9.863034149632064</v>
       </c>
       <c r="D13" t="n">
-        <v>59.62183472979462</v>
+        <v>9.688548143591627</v>
       </c>
       <c r="E13" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F13" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>94.46269356451982</v>
+        <v>15.35018770423447</v>
       </c>
       <c r="D14" t="n">
-        <v>65.22549926553165</v>
+        <v>10.59914363064889</v>
       </c>
       <c r="E14" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F14" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>86.14563696208204</v>
+        <v>13.99866600633833</v>
       </c>
       <c r="D15" t="n">
-        <v>53.64192788501521</v>
+        <v>8.716813281314971</v>
       </c>
       <c r="E15" t="n">
-        <v>28.18979933920455</v>
+        <v>4.580842392620741</v>
       </c>
       <c r="F15" t="n">
-        <v>21.36521769976825</v>
+        <v>3.47184787621234</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
